--- a/artfynd/A 26970-2026 artfynd.xlsx
+++ b/artfynd/A 26970-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043039</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043053</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043064</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043056</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043057</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043037</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043038</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1931,6 +1986,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043040</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2055,6 +2115,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043044</t>
         </is>
       </c>
     </row>
@@ -2417,6 +2492,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043048</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2541,6 +2621,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043049</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2662,6 +2747,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043050</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2783,6 +2873,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043054</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2907,6 +3002,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3018,6 +3118,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3129,6 +3234,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043051</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3240,6 +3350,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043061</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3466,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043063</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3462,6 +3582,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043041</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3573,6 +3698,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043062</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3684,8 +3814,41 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26970-2026 artfynd.xlsx
+++ b/artfynd/A 26970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135043046</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135043039</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135043047</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135043052</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135043053</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135043064</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135043056</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135043057</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>135043037</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135043038</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135043040</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135043042</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135043043</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135043044</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>135043048</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135043049</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>135043050</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135043054</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>135043058</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135043060</v>
       </c>
       <c r="B21" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135043051</v>
       </c>
       <c r="B22" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135043061</v>
       </c>
       <c r="B23" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135043063</v>
       </c>
       <c r="B24" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135043041</v>
       </c>
       <c r="B25" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>135043062</v>
       </c>
       <c r="B26" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>135043055</v>
       </c>
       <c r="B27" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26970-2026 artfynd.xlsx
+++ b/artfynd/A 26970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135043046</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135043039</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135043047</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135043052</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135043053</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135043064</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135043056</v>
       </c>
       <c r="B8" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135043060</v>
       </c>
       <c r="B21" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135043051</v>
       </c>
       <c r="B22" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135043061</v>
       </c>
       <c r="B23" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135043063</v>
       </c>
       <c r="B24" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135043041</v>
       </c>
       <c r="B25" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>135043062</v>
       </c>
       <c r="B26" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>135043055</v>
       </c>
       <c r="B27" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
